--- a/Uurrooster.xlsx
+++ b/Uurrooster.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\LUCA-3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FFDEA5B-3E82-46B9-A6C6-10E30244803A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF6C2F14-E5B8-4BF0-9BE5-0B7C1DB481E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="29" activeTab="40" xr2:uid="{28AF1FA9-2C6A-4F87-8A25-50C42A1BDAE6}"/>
   </bookViews>

--- a/Uurrooster.xlsx
+++ b/Uurrooster.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\LUCA-3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF6C2F14-E5B8-4BF0-9BE5-0B7C1DB481E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{030A9BDD-B916-4C6B-8F9E-03CECCD191B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="29" activeTab="40" xr2:uid="{28AF1FA9-2C6A-4F87-8A25-50C42A1BDAE6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="29" activeTab="36" xr2:uid="{28AF1FA9-2C6A-4F87-8A25-50C42A1BDAE6}"/>
   </bookViews>
   <sheets>
     <sheet name="Index" sheetId="1" r:id="rId1"/>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1308" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1309" uniqueCount="379">
   <si>
     <t>Vakken</t>
   </si>
@@ -1268,6 +1268,9 @@
   </si>
   <si>
     <t>10 weken voor einde stage</t>
+  </si>
+  <si>
+    <t>DEADLINE BARCELONA OPDRACHT</t>
   </si>
 </sst>
 </file>
@@ -18295,7 +18298,9 @@
     </row>
     <row r="30" spans="2:9" ht="30" x14ac:dyDescent="0.25">
       <c r="B30" s="33"/>
-      <c r="C30" s="33"/>
+      <c r="C30" s="33" t="s">
+        <v>378</v>
+      </c>
       <c r="D30" s="33"/>
       <c r="E30" s="33"/>
       <c r="F30" s="33"/>
